--- a/Meshi-Quest_システム設計書.xlsx
+++ b/Meshi-Quest_システム設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POPEYE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1F4710B-5949-4CC4-A00F-DE518825F000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E92936F8-7000-41B0-A389-26445BF4064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="822" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="822" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -22390,15 +22390,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>262754</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>186692</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>131061</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>230652</xdr:rowOff>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -22416,8 +22416,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12607154" y="424817"/>
-          <a:ext cx="1239907" cy="520210"/>
+          <a:off x="12496800" y="428625"/>
+          <a:ext cx="1524000" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22558,15 +22558,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>662609</xdr:colOff>
+      <xdr:colOff>676275</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>233442</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>124239</xdr:colOff>
+      <xdr:colOff>257175</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>37207</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -22574,6 +22574,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000006000000}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22581,8 +22584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8206409" y="471567"/>
-          <a:ext cx="1519030" cy="518140"/>
+          <a:off x="8220075" y="457200"/>
+          <a:ext cx="1638300" cy="609600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22662,15 +22665,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>287087</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>222739</xdr:rowOff>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>392206</xdr:colOff>
+      <xdr:colOff>390525</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>26504</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -22678,6 +22681,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000007000000}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22685,8 +22691,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6439116" y="458063"/>
-          <a:ext cx="1472237" cy="509735"/>
+          <a:off x="6276975" y="457200"/>
+          <a:ext cx="1657350" cy="638175"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22788,15 +22794,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>5925</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>229556</xdr:rowOff>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>394252</xdr:colOff>
+      <xdr:colOff>466725</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>33321</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -22804,6 +22810,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000008000000}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -22811,8 +22820,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4806525" y="467681"/>
-          <a:ext cx="1074127" cy="518140"/>
+          <a:off x="4829175" y="466725"/>
+          <a:ext cx="1123950" cy="600075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -24383,11 +24392,20 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000023000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000022000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
           <a:stCxn id="3" idx="2"/>
           <a:endCxn id="9" idx="0"/>
+          <a:extLst>
+            <a:ext uri="{5F17804C-33F3-41E3-A699-7DCFA2EF7971}">
+              <a16:cxnDERefs xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" st="{00000000-0008-0000-0B00-000003000000}" end="{00000000-0008-0000-0B00-000009000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -24424,13 +24442,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>297488</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>180265</xdr:rowOff>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>339647</xdr:colOff>
+      <xdr:colOff>297488</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>194582</xdr:rowOff>
     </xdr:to>
@@ -24441,16 +24459,26 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000024000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000023000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="7" idx="2"/>
           <a:endCxn id="97" idx="0"/>
+          <a:extLst>
+            <a:ext uri="{5F17804C-33F3-41E3-A699-7DCFA2EF7971}">
+              <a16:cxnDERefs xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" st="{00000000-0008-0000-0B00-000007000000}" end="{00000000-0008-0000-0B00-000061000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="7101059" y="915051"/>
-          <a:ext cx="42159" cy="7117245"/>
+        <a:xfrm>
+          <a:off x="7105650" y="1095375"/>
+          <a:ext cx="49838" cy="6719207"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -24481,13 +24509,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>49696</xdr:colOff>
+      <xdr:colOff>54665</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>37207</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>53837</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>173935</xdr:rowOff>
     </xdr:to>
@@ -24498,17 +24526,25 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000025000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000024000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="6" idx="2"/>
           <a:endCxn id="11" idx="0"/>
+          <a:extLst>
+            <a:ext uri="{5F17804C-33F3-41E3-A699-7DCFA2EF7971}">
+              <a16:cxnDERefs xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" st="{00000000-0008-0000-0B00-000006000000}" end="{00000000-0008-0000-0B00-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8965096" y="989707"/>
-          <a:ext cx="4141" cy="6804228"/>
+        <a:xfrm flipH="1">
+          <a:off x="8970065" y="1066800"/>
+          <a:ext cx="69160" cy="6727135"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -24539,13 +24575,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>185214</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>230652</xdr:rowOff>
+      <xdr:colOff>185215</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>196907</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>154469</xdr:rowOff>
     </xdr:to>
@@ -24573,8 +24609,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="13172832" y="936623"/>
-          <a:ext cx="11693" cy="6748199"/>
+          <a:off x="13215415" y="1076325"/>
+          <a:ext cx="43385" cy="6698144"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -25227,13 +25263,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>543817</xdr:colOff>
+      <xdr:colOff>576120</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>33321</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>576948</xdr:colOff>
+      <xdr:colOff>590550</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>186613</xdr:rowOff>
     </xdr:to>
@@ -25244,17 +25280,25 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000032000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000031000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="8" idx="2"/>
           <a:endCxn id="13" idx="0"/>
+          <a:extLst>
+            <a:ext uri="{5F17804C-33F3-41E3-A699-7DCFA2EF7971}">
+              <a16:cxnDERefs xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" st="{00000000-0008-0000-0B00-000008000000}" end="{00000000-0008-0000-0B00-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5344417" y="985821"/>
-          <a:ext cx="33131" cy="6820792"/>
+        <a:xfrm flipH="1">
+          <a:off x="5376720" y="1066800"/>
+          <a:ext cx="14430" cy="6739813"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -26850,15 +26894,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>179782</xdr:colOff>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>201706</xdr:rowOff>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>48088</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>10343</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -26866,6 +26910,9 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-00005A000000}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -26873,8 +26920,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10433164" y="437030"/>
-          <a:ext cx="1235424" cy="514607"/>
+          <a:off x="10372725" y="438150"/>
+          <a:ext cx="1409700" cy="628650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -26974,14 +27021,17 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-00005B000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-00005A000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10421471" y="7699836"/>
-          <a:ext cx="1235424" cy="509736"/>
+          <a:off x="10455089" y="7789483"/>
+          <a:ext cx="1239906" cy="515339"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -27137,11 +27187,11 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>102242</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>10343</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>113935</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>169483</xdr:rowOff>
     </xdr:to>
@@ -27152,17 +27202,25 @@
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-00005D000000}"/>
             </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{00000000-0008-0000-0B00-00005C000000}"/>
+            </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="90" idx="2"/>
           <a:endCxn id="91" idx="0"/>
+          <a:extLst>
+            <a:ext uri="{5F17804C-33F3-41E3-A699-7DCFA2EF7971}">
+              <a16:cxnDERefs xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" st="{00000000-0008-0000-0B00-00005A000000}" end="{00000000-0008-0000-0B00-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11075042" y="962843"/>
-          <a:ext cx="11693" cy="6826640"/>
+          <a:off x="11075042" y="1066800"/>
+          <a:ext cx="2533" cy="6722683"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -28686,7 +28744,7 @@
     <col min="1" max="1" width="3" style="6" customWidth="1"/>
     <col min="2" max="2" width="29.125" style="6" customWidth="1"/>
     <col min="3" max="3" width="31.5" style="6" customWidth="1"/>
-    <col min="4" max="4" width="119.125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="133.125" style="6" customWidth="1"/>
     <col min="5" max="16384" width="8.625" style="7"/>
   </cols>
   <sheetData>

--- a/Meshi-Quest_システム設計書.xlsx
+++ b/Meshi-Quest_システム設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\POPEYE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E92936F8-7000-41B0-A389-26445BF4064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B25667-3710-47EA-AD0C-DA43AF392330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="822" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="822" firstSheet="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -962,9 +962,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -984,9 +981,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1010,17 +1004,8 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1041,6 +1026,21 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -27655,6 +27655,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AW1"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75"/>
   <cols>
@@ -27663,7 +27666,7 @@
   <sheetData/>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -27674,936 +27677,936 @@
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="1" width="3.75" style="6" customWidth="1"/>
-    <col min="2" max="2" width="25.25" style="35" customWidth="1"/>
-    <col min="3" max="3" width="23.25" style="35" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="35" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="35" customWidth="1"/>
-    <col min="6" max="6" width="44.25" style="35" customWidth="1"/>
+    <col min="2" max="2" width="25.25" style="30" customWidth="1"/>
+    <col min="3" max="3" width="23.25" style="30" customWidth="1"/>
+    <col min="4" max="4" width="20.625" style="30" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="30" customWidth="1"/>
+    <col min="6" max="6" width="44.25" style="30" customWidth="1"/>
     <col min="7" max="16384" width="8.625" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="29" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="30" customHeight="1">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="35" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="40"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="29" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="47.25" customHeight="1">
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="35" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F10" s="40"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="35" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="35.25" customHeight="1">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F12" s="40"/>
+      <c r="F12" s="35"/>
     </row>
     <row r="13" spans="2:6" ht="34.5" customHeight="1">
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F13" s="40"/>
+      <c r="F13" s="35"/>
     </row>
     <row r="14" spans="2:6" ht="30.75" customHeight="1">
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F14" s="40"/>
+      <c r="F14" s="35"/>
     </row>
     <row r="15" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="35" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="27" customHeight="1">
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="40"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="29" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="23.25">
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="32.25" customHeight="1">
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="35" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="35" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="40"/>
+      <c r="F22" s="35"/>
     </row>
     <row r="23" spans="2:6" ht="24.75" customHeight="1">
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F23" s="40"/>
+      <c r="F23" s="35"/>
     </row>
     <row r="24" spans="2:6" ht="27" customHeight="1">
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F24" s="40"/>
+      <c r="F24" s="35"/>
     </row>
     <row r="25" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="40"/>
+      <c r="F25" s="35"/>
     </row>
     <row r="26" spans="2:6" ht="24" customHeight="1">
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F26" s="40"/>
+      <c r="F26" s="35"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="30" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="23.25">
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="30" customHeight="1">
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E30" s="38" t="s">
+      <c r="E30" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F30" s="40" t="s">
+      <c r="F30" s="35" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="D31" s="38" t="s">
+      <c r="D31" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E31" s="38" t="s">
+      <c r="E31" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="35" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="32" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E32" s="38" t="s">
+      <c r="E32" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="40"/>
+      <c r="F32" s="35"/>
     </row>
     <row r="33" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B33" s="38" t="s">
+      <c r="B33" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="38" t="s">
+      <c r="E33" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="40"/>
+      <c r="F33" s="35"/>
     </row>
     <row r="34" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B34" s="38" t="s">
+      <c r="B34" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E34" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F34" s="40"/>
+      <c r="F34" s="35"/>
     </row>
     <row r="35" spans="2:6" ht="25.5" customHeight="1">
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="D35" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="E35" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F35" s="40"/>
+      <c r="F35" s="35"/>
     </row>
     <row r="36" spans="2:6" ht="27" customHeight="1">
-      <c r="B36" s="38" t="s">
+      <c r="B36" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="E36" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F36" s="40"/>
+      <c r="F36" s="35"/>
     </row>
     <row r="37" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="D37" s="38" t="s">
+      <c r="D37" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E37" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F37" s="40"/>
+      <c r="F37" s="35"/>
     </row>
     <row r="38" spans="2:6" ht="37.5" customHeight="1">
-      <c r="B38" s="38" t="s">
+      <c r="B38" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E38" s="38" t="s">
+      <c r="E38" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="35" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="D39" s="38" t="s">
+      <c r="D39" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="F39" s="35" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="29" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="23.25">
-      <c r="B42" s="36" t="s">
+      <c r="B42" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="E42" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="35.25" customHeight="1">
-      <c r="B43" s="38" t="s">
+      <c r="B43" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="D43" s="38" t="s">
+      <c r="D43" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="40" t="s">
+      <c r="F43" s="35" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B44" s="38" t="s">
+      <c r="B44" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="38" t="s">
+      <c r="D44" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E44" s="38" t="s">
+      <c r="E44" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="40" t="s">
+      <c r="F44" s="35" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="33" customHeight="1">
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="38" t="s">
+      <c r="E45" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F45" s="40"/>
+      <c r="F45" s="35"/>
     </row>
     <row r="46" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B46" s="38" t="s">
+      <c r="B46" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="D46" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="E46" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F46" s="40"/>
+      <c r="F46" s="35"/>
     </row>
     <row r="47" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B47" s="38" t="s">
+      <c r="B47" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D47" s="38" t="s">
+      <c r="D47" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="38" t="s">
+      <c r="E47" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F47" s="40"/>
+      <c r="F47" s="35"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="34" t="s">
+      <c r="B49" s="29" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="36" t="s">
+      <c r="E50" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F50" s="37" t="s">
+      <c r="F50" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.25" customHeight="1">
-      <c r="B51" s="38" t="s">
+      <c r="B51" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D51" s="38" t="s">
+      <c r="D51" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E51" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F51" s="40" t="s">
+      <c r="F51" s="35" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B52" s="38" t="s">
+      <c r="B52" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="39" t="s">
+      <c r="C52" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D52" s="38" t="s">
+      <c r="D52" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E52" s="38" t="s">
+      <c r="E52" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F52" s="40" t="s">
+      <c r="F52" s="35" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="55.5" customHeight="1">
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E53" s="38" t="s">
+      <c r="E53" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F53" s="40" t="s">
+      <c r="F53" s="35" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="36" customHeight="1">
-      <c r="B54" s="38" t="s">
+      <c r="B54" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="D54" s="38" t="s">
+      <c r="D54" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="38" t="s">
+      <c r="E54" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F54" s="40" t="s">
+      <c r="F54" s="35" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="30.75" customHeight="1">
-      <c r="B55" s="38" t="s">
+      <c r="B55" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="D55" s="38" t="s">
+      <c r="D55" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F55" s="40"/>
+      <c r="F55" s="35"/>
     </row>
     <row r="56" spans="2:6" ht="34.5" customHeight="1">
-      <c r="B56" s="38" t="s">
+      <c r="B56" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F56" s="40"/>
+      <c r="F56" s="35"/>
     </row>
     <row r="57" spans="2:6" ht="30.75" customHeight="1">
-      <c r="B57" s="38" t="s">
+      <c r="B57" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="E57" s="38" t="s">
+      <c r="E57" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F57" s="40"/>
+      <c r="F57" s="35"/>
     </row>
     <row r="58" spans="2:6" ht="33" customHeight="1">
-      <c r="B58" s="38" t="s">
+      <c r="B58" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="D58" s="38" t="s">
+      <c r="D58" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="E58" s="38" t="s">
+      <c r="E58" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F58" s="40"/>
+      <c r="F58" s="35"/>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="34" t="s">
+      <c r="B60" s="29" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="23.25">
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D61" s="36" t="s">
+      <c r="D61" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E61" s="36" t="s">
+      <c r="E61" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F61" s="37" t="s">
+      <c r="F61" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="32.25" customHeight="1">
-      <c r="B62" s="38" t="s">
+      <c r="B62" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="38" t="s">
+      <c r="D62" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="38" t="s">
+      <c r="E62" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F62" s="40" t="s">
+      <c r="F62" s="35" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="63" spans="2:6" ht="74.25" customHeight="1">
-      <c r="B63" s="38" t="s">
+      <c r="B63" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="38" t="s">
+      <c r="D63" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E63" s="38" t="s">
+      <c r="E63" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F63" s="40" t="s">
+      <c r="F63" s="35" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="64" spans="2:6" ht="57.75" customHeight="1">
-      <c r="B64" s="38" t="s">
+      <c r="B64" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="D64" s="38" t="s">
+      <c r="D64" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E64" s="38" t="s">
+      <c r="E64" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F64" s="40" t="s">
+      <c r="F64" s="35" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="65" spans="2:6" ht="40.5" customHeight="1">
-      <c r="B65" s="38" t="s">
+      <c r="B65" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F65" s="40"/>
+      <c r="F65" s="35"/>
     </row>
     <row r="67" spans="2:6">
-      <c r="B67" s="34" t="s">
+      <c r="B67" s="29" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="23.25">
-      <c r="B68" s="36" t="s">
+      <c r="B68" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C68" s="36" t="s">
+      <c r="C68" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D68" s="36" t="s">
+      <c r="D68" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="E68" s="36" t="s">
+      <c r="E68" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="F68" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="69" spans="2:6" ht="51" customHeight="1">
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="33" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="39" t="s">
+      <c r="C69" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="D69" s="38" t="s">
+      <c r="D69" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="E69" s="38" t="s">
+      <c r="E69" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F69" s="40" t="s">
+      <c r="F69" s="35" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="70" spans="2:6" ht="74.25" customHeight="1">
-      <c r="B70" s="38" t="s">
+      <c r="B70" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="39" t="s">
+      <c r="C70" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D70" s="38" t="s">
+      <c r="D70" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="E70" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="F70" s="40" t="s">
+      <c r="F70" s="35" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="71" spans="2:6" ht="38.25" customHeight="1">
-      <c r="B71" s="38" t="s">
+      <c r="B71" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="C71" s="39" t="s">
+      <c r="C71" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D71" s="38" t="s">
+      <c r="D71" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="F71" s="40"/>
+      <c r="F71" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -28680,38 +28683,38 @@
       </c>
     </row>
     <row r="5" spans="2:3" ht="84.75" customHeight="1">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="111.75" customHeight="1">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="39.75" customHeight="1">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="35.25" customHeight="1">
-      <c r="B8" s="15"/>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="42" customHeight="1">
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="17" t="s">
         <v>13</v>
       </c>
     </row>
@@ -28719,12 +28722,12 @@
       <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:3">
-      <c r="C12" s="19"/>
+      <c r="C12" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28749,109 +28752,109 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" ht="28.5" customHeight="1">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="30.75" customHeight="1">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="65.25" customHeight="1">
-      <c r="B4" s="21"/>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="72.75" customHeight="1">
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="33.75" customHeight="1">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="31.5" customHeight="1">
-      <c r="B7" s="21"/>
-      <c r="C7" s="22" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="63.75" customHeight="1">
-      <c r="B8" s="21"/>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="28.5" customHeight="1">
-      <c r="B9" s="21"/>
-      <c r="C9" s="22" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="56.25" customHeight="1">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="29.25" customHeight="1">
-      <c r="B11" s="21"/>
-      <c r="C11" s="22" t="s">
+      <c r="B11" s="37"/>
+      <c r="C11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="22" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="30" customHeight="1">
-      <c r="B12" s="21"/>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="37"/>
+      <c r="C12" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="24" t="s">
         <v>41</v>
       </c>
     </row>
@@ -34796,398 +34799,392 @@
     <col min="2" max="2" width="21.875" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.125" style="6" customWidth="1"/>
     <col min="4" max="4" width="21.875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="67.25" style="6" customWidth="1"/>
+    <col min="5" max="5" width="73" style="6" customWidth="1"/>
     <col min="6" max="6" width="11.375" style="6" customWidth="1"/>
     <col min="7" max="16384" width="8.625" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="25" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="42" customHeight="1">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="40">
         <v>3000</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B4" s="29"/>
-      <c r="C4" s="33" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="32"/>
+      <c r="F4" s="40"/>
     </row>
     <row r="5" spans="2:6" ht="31.5" customHeight="1">
-      <c r="B5" s="29"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="30" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="32"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B6" s="29"/>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="32"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="2:6" ht="26.25" customHeight="1">
-      <c r="B7" s="29"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="30" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="32"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="2:6" ht="24" customHeight="1">
-      <c r="B8" s="29"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="30" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="32"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B9" s="29"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="30" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="32"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="2:6" ht="33" customHeight="1">
-      <c r="B10" s="29"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="30" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="32"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="2:6" ht="42" customHeight="1">
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="32"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B12" s="29"/>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="32"/>
+      <c r="F12" s="40"/>
     </row>
     <row r="13" spans="2:6" ht="27" customHeight="1">
-      <c r="B13" s="29"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="30" t="s">
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="32"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B14" s="29"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="30" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="32"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="2:6" ht="24.75" customHeight="1">
-      <c r="B15" s="29"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="30" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="32"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B16" s="29"/>
-      <c r="C16" s="33" t="s">
+      <c r="B16" s="38"/>
+      <c r="C16" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="32"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B17" s="29"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="30" t="s">
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="32"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B18" s="29"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="30" t="s">
+      <c r="B18" s="38"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="32"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B19" s="29"/>
-      <c r="C19" s="30" t="s">
+      <c r="B19" s="38"/>
+      <c r="C19" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="32"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="20" spans="2:6" ht="42" customHeight="1">
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="40">
         <v>4000</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="25.5" customHeight="1">
-      <c r="B21" s="29"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="30" t="s">
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="32"/>
+      <c r="F21" s="40"/>
     </row>
     <row r="22" spans="2:6" ht="29.25" customHeight="1">
-      <c r="B22" s="29"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="30" t="s">
+      <c r="B22" s="38"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="32"/>
+      <c r="F22" s="40"/>
     </row>
     <row r="23" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B23" s="29"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="30" t="s">
+      <c r="B23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="40"/>
     </row>
     <row r="24" spans="2:6" ht="24.75" customHeight="1">
-      <c r="B24" s="29"/>
-      <c r="C24" s="33" t="s">
+      <c r="B24" s="38"/>
+      <c r="C24" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="32"/>
+      <c r="F24" s="40"/>
     </row>
     <row r="25" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B25" s="29"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="30" t="s">
+      <c r="B25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="32"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B26" s="29"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="30" t="s">
+      <c r="B26" s="38"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="32"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" spans="2:6" ht="34.5" customHeight="1">
-      <c r="B27" s="29"/>
-      <c r="C27" s="33" t="s">
+      <c r="B27" s="38"/>
+      <c r="C27" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F27" s="32"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="2:6" ht="30" customHeight="1">
-      <c r="B28" s="29"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="30" t="s">
+      <c r="B28" s="38"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="F28" s="32"/>
+      <c r="F28" s="40"/>
     </row>
     <row r="29" spans="2:6" ht="24.75" customHeight="1">
-      <c r="B29" s="29"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="30" t="s">
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="32"/>
+      <c r="F29" s="40"/>
     </row>
     <row r="30" spans="2:6" ht="28.5" customHeight="1">
-      <c r="B30" s="29"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="30" t="s">
+      <c r="B30" s="38"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="F30" s="32"/>
+      <c r="F30" s="40"/>
     </row>
     <row r="31" spans="2:6" ht="24.75" customHeight="1">
-      <c r="B31" s="29"/>
-      <c r="C31" s="33" t="s">
+      <c r="B31" s="38"/>
+      <c r="C31" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="31" t="s">
+      <c r="E31" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="F31" s="32"/>
+      <c r="F31" s="40"/>
     </row>
     <row r="32" spans="2:6" ht="30" customHeight="1">
-      <c r="B32" s="29"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="30" t="s">
+      <c r="B32" s="38"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B20:B32"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="F20:F32"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="C31:C32"/>
     <mergeCell ref="B3:B10"/>
     <mergeCell ref="F3:F19"/>
     <mergeCell ref="C4:C5"/>
@@ -35195,6 +35192,12 @@
     <mergeCell ref="B11:B19"/>
     <mergeCell ref="C12:C15"/>
     <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B20:B32"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="F20:F32"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="C31:C32"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
